--- a/data/trans_orig/IP74A6_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP74A6_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto según si ha resuelto los pagos de recibos de agua, gas, calefacción, electricidad, comunidad en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Adultos según si tienen resuelto el retraso en los pagos de recibos de agua, gas, calefacción, electricidad, comunidad en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>14052</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22114</t>
+          <t>21486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27650</t>
+          <t>27786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>566</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>819</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6983</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>24,53%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9794</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16080</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>19126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25547</t>
+          <t>25575</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31240</t>
+          <t>31549</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>40464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7470</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>12944</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9233</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16234</t>
+          <t>16315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,43%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,22%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43861</t>
+          <t>44336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53091</t>
+          <t>53196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50829</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61566</t>
+          <t>61814</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>99120</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112359</t>
+          <t>112531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14259</t>
+          <t>13784</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>13870</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25273</t>
+          <t>25097</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
